--- a/sample-emp.xlsx
+++ b/sample-emp.xlsx
@@ -439,7 +439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B2" t="str">
         <v>A001</v>
@@ -477,7 +477,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B3" t="str">
         <v>A002</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B4" t="str">
         <v>A003</v>
@@ -553,7 +553,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B5" t="str">
         <v>A004</v>
@@ -591,7 +591,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B6" t="str">
         <v>A005</v>
@@ -629,7 +629,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B7" t="str">
         <v>A006</v>
@@ -667,7 +667,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B8" t="str">
         <v>A007</v>
@@ -705,7 +705,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B9" t="str">
         <v>A008</v>
@@ -743,7 +743,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B10" t="str">
         <v>A009</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B11" t="str">
         <v>A010</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B12" t="str">
         <v>A011</v>
@@ -857,7 +857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B13" t="str">
         <v>A012</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B14" t="str">
         <v>A013</v>
@@ -933,7 +933,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B15" t="str">
         <v>A014</v>
@@ -971,7 +971,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B16" t="str">
         <v>A015</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B17" t="str">
         <v>A016</v>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B18" t="str">
         <v>A017</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B19" t="str">
         <v>A018</v>
@@ -1123,7 +1123,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B20" t="str">
         <v>A019</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B21" t="str">
         <v>A020</v>
@@ -1199,7 +1199,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B22" t="str">
         <v>A021</v>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B23" t="str">
         <v>A022</v>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B24" t="str">
         <v>A023</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>11/03</v>
+        <v>10/03</v>
       </c>
       <c r="B25" t="str">
         <v>A024</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B26" t="str">
         <v>B001</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B27" t="str">
         <v>B002</v>
@@ -1427,7 +1427,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B28" t="str">
         <v>B003</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B29" t="str">
         <v>B004</v>
@@ -1503,7 +1503,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B30" t="str">
         <v>B005</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B31" t="str">
         <v>B006</v>
@@ -1579,7 +1579,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B32" t="str">
         <v>B007</v>
@@ -1617,7 +1617,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B33" t="str">
         <v>B008</v>
@@ -1655,7 +1655,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B34" t="str">
         <v>B009</v>
@@ -1693,7 +1693,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B35" t="str">
         <v>B010</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B36" t="str">
         <v>B011</v>
@@ -1769,7 +1769,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B37" t="str">
         <v>B012</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B38" t="str">
         <v>B013</v>
@@ -1845,7 +1845,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B39" t="str">
         <v>B014</v>
@@ -1883,7 +1883,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B40" t="str">
         <v>B015</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B41" t="str">
         <v>B016</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B42" t="str">
         <v>B017</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B43" t="str">
         <v>B018</v>
@@ -2035,7 +2035,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B44" t="str">
         <v>B019</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B45" t="str">
         <v>B020</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B46" t="str">
         <v>B021</v>
@@ -2149,7 +2149,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B47" t="str">
         <v>B022</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B48" t="str">
         <v>B023</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>11/10</v>
+        <v>10/11</v>
       </c>
       <c r="B49" t="str">
         <v>B024</v>

--- a/sample-emp.xlsx
+++ b/sample-emp.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:M49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,6 +436,9 @@
       <c r="L1" t="str">
         <v>報到時間</v>
       </c>
+      <c r="M1" t="str">
+        <v>車號</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -474,6 +477,9 @@
       <c r="L2" t="str">
         <v/>
       </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -512,6 +518,9 @@
       <c r="L3" t="str">
         <v/>
       </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -550,6 +559,9 @@
       <c r="L4" t="str">
         <v/>
       </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -588,6 +600,9 @@
       <c r="L5" t="str">
         <v/>
       </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -626,6 +641,9 @@
       <c r="L6" t="str">
         <v/>
       </c>
+      <c r="M6" t="str">
+        <v>ABC-1005</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -664,6 +682,9 @@
       <c r="L7" t="str">
         <v/>
       </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -702,6 +723,9 @@
       <c r="L8" t="str">
         <v/>
       </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -740,6 +764,9 @@
       <c r="L9" t="str">
         <v/>
       </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -778,6 +805,9 @@
       <c r="L10" t="str">
         <v/>
       </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -816,6 +846,9 @@
       <c r="L11" t="str">
         <v/>
       </c>
+      <c r="M11" t="str">
+        <v>ABC-1010</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -854,6 +887,9 @@
       <c r="L12" t="str">
         <v/>
       </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -892,6 +928,9 @@
       <c r="L13" t="str">
         <v/>
       </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -930,6 +969,9 @@
       <c r="L14" t="str">
         <v/>
       </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -968,6 +1010,9 @@
       <c r="L15" t="str">
         <v/>
       </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1006,6 +1051,9 @@
       <c r="L16" t="str">
         <v/>
       </c>
+      <c r="M16" t="str">
+        <v>ABC-1015</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1044,6 +1092,9 @@
       <c r="L17" t="str">
         <v/>
       </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1082,6 +1133,9 @@
       <c r="L18" t="str">
         <v/>
       </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1120,6 +1174,9 @@
       <c r="L19" t="str">
         <v/>
       </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1158,6 +1215,9 @@
       <c r="L20" t="str">
         <v/>
       </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1196,6 +1256,9 @@
       <c r="L21" t="str">
         <v/>
       </c>
+      <c r="M21" t="str">
+        <v>ABC-1020</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1234,6 +1297,9 @@
       <c r="L22" t="str">
         <v/>
       </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1272,6 +1338,9 @@
       <c r="L23" t="str">
         <v/>
       </c>
+      <c r="M23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1310,6 +1379,9 @@
       <c r="L24" t="str">
         <v/>
       </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1348,6 +1420,9 @@
       <c r="L25" t="str">
         <v/>
       </c>
+      <c r="M25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1386,6 +1461,9 @@
       <c r="L26" t="str">
         <v/>
       </c>
+      <c r="M26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1424,6 +1502,9 @@
       <c r="L27" t="str">
         <v/>
       </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1462,6 +1543,9 @@
       <c r="L28" t="str">
         <v/>
       </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1500,6 +1584,9 @@
       <c r="L29" t="str">
         <v/>
       </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1538,6 +1625,9 @@
       <c r="L30" t="str">
         <v/>
       </c>
+      <c r="M30" t="str">
+        <v>XYZ-1005</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1576,6 +1666,9 @@
       <c r="L31" t="str">
         <v/>
       </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1614,6 +1707,9 @@
       <c r="L32" t="str">
         <v/>
       </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1652,6 +1748,9 @@
       <c r="L33" t="str">
         <v/>
       </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1690,6 +1789,9 @@
       <c r="L34" t="str">
         <v/>
       </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -1728,6 +1830,9 @@
       <c r="L35" t="str">
         <v/>
       </c>
+      <c r="M35" t="str">
+        <v>XYZ-1010</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1766,6 +1871,9 @@
       <c r="L36" t="str">
         <v/>
       </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1804,6 +1912,9 @@
       <c r="L37" t="str">
         <v/>
       </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -1842,6 +1953,9 @@
       <c r="L38" t="str">
         <v/>
       </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -1880,6 +1994,9 @@
       <c r="L39" t="str">
         <v/>
       </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -1918,6 +2035,9 @@
       <c r="L40" t="str">
         <v/>
       </c>
+      <c r="M40" t="str">
+        <v>XYZ-1015</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1956,6 +2076,9 @@
       <c r="L41" t="str">
         <v/>
       </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -1994,6 +2117,9 @@
       <c r="L42" t="str">
         <v/>
       </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -2032,6 +2158,9 @@
       <c r="L43" t="str">
         <v/>
       </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2070,6 +2199,9 @@
       <c r="L44" t="str">
         <v/>
       </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2108,6 +2240,9 @@
       <c r="L45" t="str">
         <v/>
       </c>
+      <c r="M45" t="str">
+        <v>XYZ-1020</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -2146,6 +2281,9 @@
       <c r="L46" t="str">
         <v/>
       </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -2184,6 +2322,9 @@
       <c r="L47" t="str">
         <v/>
       </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -2222,6 +2363,9 @@
       <c r="L48" t="str">
         <v/>
       </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2260,10 +2404,13 @@
       <c r="L49" t="str">
         <v/>
       </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M49"/>
   </ignoredErrors>
 </worksheet>
 </file>